--- a/conferences/conferences.xlsx
+++ b/conferences/conferences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kuleuven-my.sharepoint.com/personal/lasai_barrenadataleb_kuleuven_be/Documents/Documentos e informacion/Trabajo/Webpage_quarto/conferences/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="11_F25DC773A252ABDACC10489D719C6A665ADE58F5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4993045B-4CC6-4E32-8925-A177CAB2573F}"/>
+  <xr:revisionPtr revIDLastSave="105" documentId="11_F25DC773A252ABDACC10489D719C6A665ADE58F5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A16C359F-1C30-425E-B75F-D7E019502747}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="37">
   <si>
     <t>Location</t>
   </si>
@@ -63,7 +63,79 @@
     <t>Budapest</t>
   </si>
   <si>
-    <t>Thessaloniki </t>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thessaloniki </t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Poster</t>
+  </si>
+  <si>
+    <t>Presentation</t>
+  </si>
+  <si>
+    <t>Head-to-head comparisons of RMI and ADNEX model to diagnose ovarian malignancy: systematic review and meta-analysis</t>
+  </si>
+  <si>
+    <t>Multicenter flexible calibration curves with binary outcomes using random effects meta-analysis</t>
+  </si>
+  <si>
+    <t>Drawing multicenter calibration curves</t>
+  </si>
+  <si>
+    <t>The ADNEX model for ovarian cancer diagnosis: a systematic review and meta-analysis of external validation studies</t>
+  </si>
+  <si>
+    <t>Do we understand random forests?</t>
+  </si>
+  <si>
+    <t>Conference name</t>
+  </si>
+  <si>
+    <t>International Society of Ultrasound in Obstetrics and Gynecology</t>
+  </si>
+  <si>
+    <t>International Society of clinical biostatistics</t>
+  </si>
+  <si>
+    <t>Young statisticians meeting</t>
+  </si>
+  <si>
+    <t>Sociedad española de bioestadistica</t>
+  </si>
+  <si>
+    <t>Link_1_name</t>
+  </si>
+  <si>
+    <t>Link_2_name</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
+    <t>https://github.com/LasaiBarrenada/web_resources/blob/6620d40724dd436b0f2825cd91cad5181813a304/DRAWING%20MULTICENTER%20CALIBRATION%20CURVES%20w.pdf</t>
+  </si>
+  <si>
+    <t>https://obgyn.onlinelibrary.wiley.com/doi/10.1002/uog.26336</t>
+  </si>
+  <si>
+    <t>https://github.com/LasaiBarrenada/web_resources/blob/6620d40724dd436b0f2825cd91cad5181813a304/202310%20ISUOG%20Seul.pptx</t>
+  </si>
+  <si>
+    <t>https://github.com/LasaiBarrenada/web_resources/blob/6620d40724dd436b0f2825cd91cad5181813a304/PosterLasai_YSM.pdf</t>
+  </si>
+  <si>
+    <t>Link_1</t>
+  </si>
+  <si>
+    <t>Link_2</t>
   </si>
 </sst>
 </file>
@@ -385,90 +457,232 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" customWidth="1"/>
+    <col min="8" max="8" width="12.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
+      <c r="F1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K1" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="C2">
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2">
         <v>2023</v>
       </c>
+      <c r="F2">
+        <v>7</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
         <v>6</v>
       </c>
-      <c r="C3">
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3">
         <v>2023</v>
       </c>
+      <c r="F3">
+        <v>8</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="C4">
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4">
         <v>2023</v>
       </c>
+      <c r="F4">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
       <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
         <v>10</v>
       </c>
-      <c r="C5">
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5">
         <v>2024</v>
       </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
         <v>6</v>
       </c>
-      <c r="C6">
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6">
         <v>2024</v>
       </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
       <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
         <v>8</v>
       </c>
-      <c r="C7">
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7">
         <v>2024</v>
+      </c>
+      <c r="F7">
+        <v>9</v>
+      </c>
+      <c r="G7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K7">
+    <sortCondition ref="E2:E7"/>
+    <sortCondition ref="F2:F7"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>